--- a/Config/Excel/GameConfig/EmitterEffectPackConfig.xlsx
+++ b/Config/Excel/GameConfig/EmitterEffectPackConfig.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BuffGroupConfig" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuffGroupConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1028,7 +1028,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1112,8 +1117,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4"/>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>80001</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -1121,7 +1125,7 @@
           <t>CD减少50%</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>70001</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -1131,27 +1135,25 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5"/>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>80002</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>伤害+50%</t>
-        </is>
-      </c>
-      <c r="D5">
+          <t>基础伤害+50%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>70002</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>单个属性修饰：白值伤害倍率提升</t>
+          <t>单个属性修饰：基础伤害提升</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6"/>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>80003</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -1159,7 +1161,7 @@
           <t>射程+30%</t>
         </is>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>70003</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -1169,8 +1171,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7"/>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>80004</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -1178,7 +1179,7 @@
           <t>击退1米</t>
         </is>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>71001</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -1188,8 +1189,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8"/>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>80005</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -1197,7 +1197,7 @@
           <t>冻结0.5秒</t>
         </is>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>71002</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -1207,8 +1207,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9"/>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>80006</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -1216,7 +1215,7 @@
           <t>减速30%</t>
         </is>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>71003</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -1226,8 +1225,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10"/>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>80007</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -1235,7 +1233,7 @@
           <t>毒伤DOT</t>
         </is>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>71004</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -1245,8 +1243,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11"/>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>80008</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -1266,8 +1263,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12"/>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>80009</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,8 +1283,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13"/>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>80010</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -1308,8 +1303,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14"/>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>80011</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1329,8 +1323,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15"/>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>80012</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -1350,5 +1343,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>